--- a/numbers.xlsx
+++ b/numbers.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saadatdost.majid\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saadatdost.majid\Desktop\Digital\phone numbers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB5A7D1-CF5F-4E17-AD88-ED4B48AED139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172178DB-897B-4A20-91EE-1CCD1F86DFE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A04015D6-22AB-4A16-AB13-6D462801A42C}"/>
   </bookViews>
@@ -1883,10 +1883,10 @@
         <v>102</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>159</v>
